--- a/table/Tables.xlsx
+++ b/table/Tables.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10511"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annabethlu/Projects/ded-dep-ibs/table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4694AEF9-CAF0-2E44-8415-F0AA21E2EBF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA77450-140E-CA40-AF03-E45B3F95ADF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="920" yWindow="760" windowWidth="28480" windowHeight="18360" activeTab="1" xr2:uid="{D515C405-0CB0-4046-88E1-6357459E1EB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
     <sheet name="1" sheetId="3" r:id="rId2"/>
-    <sheet name="2" sheetId="26" r:id="rId3"/>
+    <sheet name="2" sheetId="27" r:id="rId3"/>
     <sheet name="3" sheetId="24" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="230">
   <si>
     <t>Genome-wide Association Study (GWAS)</t>
   </si>
@@ -780,9 +780,6 @@
     <t>Genes Prioritized by Positional, eQTL and Chromatin Interaction Mappings</t>
   </si>
   <si>
-    <t>Table 2. Genes Prioritized by Positional, eQTL and Chromatin Interaction Mappings</t>
-  </si>
-  <si>
     <t>Table 1. Demographic Information of Participants</t>
   </si>
   <si>
@@ -795,287 +792,6 @@
     <t>Mendelian Randomization Results of the Tested Conditions</t>
   </si>
   <si>
-    <t>symbol</t>
-  </si>
-  <si>
-    <t>chr</t>
-  </si>
-  <si>
-    <t>start</t>
-  </si>
-  <si>
-    <t>end</t>
-  </si>
-  <si>
-    <t>strand</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>IndSigSNPs</t>
-  </si>
-  <si>
-    <t>ENSG00000124019</t>
-  </si>
-  <si>
-    <t>FAM124B</t>
-  </si>
-  <si>
-    <t>Left_Ventricle:Liver:GM12878:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>rs4624371</t>
-  </si>
-  <si>
-    <t>ENSG00000036257</t>
-  </si>
-  <si>
-    <t>CUL3</t>
-  </si>
-  <si>
-    <t>+</t>
-  </si>
-  <si>
-    <t>Adult_Cortex:Fetal_Cortex:Aorta:Left_Ventricle:Liver:GM12878:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>ENSG00000228446</t>
-  </si>
-  <si>
-    <t>AC073052.1</t>
-  </si>
-  <si>
-    <t>pseudogene</t>
-  </si>
-  <si>
-    <t>Aorta:Left_Ventricle:Liver:GM12878:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>ENSG00000105993</t>
-  </si>
-  <si>
-    <t>DNAJB6</t>
-  </si>
-  <si>
-    <t>IMR90</t>
-  </si>
-  <si>
-    <t>rs9692250</t>
-  </si>
-  <si>
-    <t>ENSG00000074201</t>
-  </si>
-  <si>
-    <t>CLNS1A</t>
-  </si>
-  <si>
-    <t>Promoter_anchored_loops:IMR90</t>
-  </si>
-  <si>
-    <t>rs687037</t>
-  </si>
-  <si>
-    <t>ENSG00000178301</t>
-  </si>
-  <si>
-    <t>AQP11</t>
-  </si>
-  <si>
-    <t>IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>Promoter_anchored_loops:Mesenchymal_Stem_Cell</t>
-  </si>
-  <si>
-    <t>ENSG00000254985</t>
-  </si>
-  <si>
-    <t>RSF1-IT2</t>
-  </si>
-  <si>
-    <t>sense_intronic</t>
-  </si>
-  <si>
-    <t>ENSG00000087884</t>
-  </si>
-  <si>
-    <t>AAMDC</t>
-  </si>
-  <si>
-    <t>ENSG00000254459</t>
-  </si>
-  <si>
-    <t>RP11-91P24.7</t>
-  </si>
-  <si>
-    <t>antisense</t>
-  </si>
-  <si>
-    <t>IMR90:Mesenchymal_Stem_Cell:Mesendoderm:hESC</t>
-  </si>
-  <si>
-    <t>ENSG00000254691</t>
-  </si>
-  <si>
-    <t>RP11-91P24.5</t>
-  </si>
-  <si>
-    <t>Promoter_anchored_loops:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:hESC</t>
-  </si>
-  <si>
-    <t>ENSG00000255449</t>
-  </si>
-  <si>
-    <t>RP11-91P24.6</t>
-  </si>
-  <si>
-    <t>ENSG00000241782</t>
-  </si>
-  <si>
-    <t>RP11-91P24.1</t>
-  </si>
-  <si>
-    <t>ENSG00000149262</t>
-  </si>
-  <si>
-    <t>INTS4</t>
-  </si>
-  <si>
-    <t>Adult_Cortex:Fetal_Cortex:Left_Ventricle:Liver:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>rs927751</t>
-  </si>
-  <si>
-    <t>ENSG00000179133</t>
-  </si>
-  <si>
-    <t>C10orf67</t>
-  </si>
-  <si>
-    <t>ENSG00000224215</t>
-  </si>
-  <si>
-    <t>RP11-371A19.2</t>
-  </si>
-  <si>
-    <t>ENSG00000145349</t>
-  </si>
-  <si>
-    <t>CAMK2D</t>
-  </si>
-  <si>
-    <t>rs2040744</t>
-  </si>
-  <si>
-    <t>ENSG00000188107</t>
-  </si>
-  <si>
-    <t>EYS</t>
-  </si>
-  <si>
-    <t>Aorta:Liver:Mesenchymal_Stem_Cell:Mesendoderm:hESC</t>
-  </si>
-  <si>
-    <t>rs12663968</t>
-  </si>
-  <si>
-    <t>ENSG00000147408</t>
-  </si>
-  <si>
-    <t>CSGALNACT1</t>
-  </si>
-  <si>
-    <t>Adult_Cortex:Left_Ventricle:IMR90:Mesenchymal_Stem_Cell:Mesendoderm:Trophoblast-like_Cell:hESC</t>
-  </si>
-  <si>
-    <t>rs4332151</t>
-  </si>
-  <si>
-    <t>ENSG00000157450</t>
-  </si>
-  <si>
-    <t>RNF111</t>
-  </si>
-  <si>
-    <t>Trophoblast-like_Cell</t>
-  </si>
-  <si>
-    <t>rs34868598</t>
-  </si>
-  <si>
-    <t>Inflammatory Bowel Disease</t>
-  </si>
-  <si>
-    <t>ENSG</t>
-  </si>
-  <si>
-    <t>MAGMA</t>
-  </si>
-  <si>
-    <t>Positional Mapping</t>
-  </si>
-  <si>
-    <t>eQTL Mapping</t>
-  </si>
-  <si>
-    <t>Chromatin Interaction Mapping</t>
-  </si>
-  <si>
-    <t>Z</t>
-  </si>
-  <si>
-    <t>p</t>
-  </si>
-  <si>
-    <t>Max CADD</t>
-  </si>
-  <si>
-    <t>Map</t>
-  </si>
-  <si>
-    <t>protein coding</t>
-  </si>
-  <si>
-    <t>+/–</t>
-  </si>
-  <si>
-    <t>–</t>
-  </si>
-  <si>
-    <r>
-      <t>N</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>SNP</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Min </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>p</t>
-    </r>
-  </si>
-  <si>
-    <t>Min Q</t>
-  </si>
-  <si>
     <t>8.96% (152)</t>
   </si>
   <si>
@@ -1085,13 +801,13 @@
     <t>12.97% (220)</t>
   </si>
   <si>
-    <t>13.59 (620)</t>
-  </si>
-  <si>
-    <t>Case (n= 9353)</t>
-  </si>
-  <si>
     <t>Control (n= 18835)</t>
+  </si>
+  <si>
+    <t>Case (n= 1226)</t>
+  </si>
+  <si>
+    <t>13.59% (620)</t>
   </si>
 </sst>
 </file>
@@ -1102,7 +818,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1184,13 +900,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <i/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1200,7 +909,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1303,48 +1012,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1352,7 +1019,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1459,57 +1126,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1528,13 +1144,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1913,7 +1526,7 @@
         <v>216</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.2">
@@ -1929,7 +1542,7 @@
         <v>218</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
   </sheetData>
@@ -1958,7 +1571,7 @@
   <sheetData>
     <row r="1" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B1" s="12"/>
       <c r="C1" s="12"/>
@@ -1968,28 +1581,28 @@
       <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="40" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54" t="s">
+      <c r="C2" s="37"/>
+      <c r="D2" s="37"/>
+      <c r="E2" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
+      <c r="F2" s="37"/>
+      <c r="G2" s="37"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="58"/>
+      <c r="A3" s="41"/>
       <c r="B3" s="31" t="s">
-        <v>315</v>
+        <v>228</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>316</v>
+        <v>227</v>
       </c>
       <c r="D3" s="31" t="s">
         <v>213</v>
@@ -2086,23 +1699,23 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="55" t="s">
+      <c r="A8" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="54"/>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54" t="s">
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="54"/>
-      <c r="G8" s="54"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="37"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="56"/>
+      <c r="A9" s="39"/>
       <c r="B9" s="31" t="s">
         <v>185</v>
       </c>
@@ -2176,7 +1789,7 @@
         <v>212</v>
       </c>
       <c r="B12" s="28" t="s">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="C12" s="28" t="s">
         <v>16</v>
@@ -2194,7 +1807,7 @@
         <v>211</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>312</v>
+        <v>225</v>
       </c>
       <c r="C13" s="32" t="s">
         <v>16</v>
@@ -2208,23 +1821,23 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="54" t="s">
+      <c r="B14" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="54"/>
-      <c r="D14" s="54"/>
-      <c r="E14" s="54" t="s">
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="54"/>
-      <c r="G14" s="54"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56"/>
+      <c r="A15" s="39"/>
       <c r="B15" s="31" t="s">
         <v>170</v>
       </c>
@@ -2298,7 +1911,7 @@
         <v>212</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>313</v>
+        <v>226</v>
       </c>
       <c r="C18" s="28" t="s">
         <v>16</v>
@@ -2316,7 +1929,7 @@
         <v>214</v>
       </c>
       <c r="B19" s="32" t="s">
-        <v>311</v>
+        <v>224</v>
       </c>
       <c r="C19" s="32" t="s">
         <v>16</v>
@@ -2431,1182 +2044,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3DC725E-FE52-F14B-9308-0585E30E9573}">
-  <dimension ref="A1:R25"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="17" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="5" customWidth="1"/>
-    <col min="11" max="13" width="10.83203125" style="5"/>
-    <col min="14" max="14" width="6.83203125" style="41" customWidth="1"/>
-    <col min="15" max="15" width="7.1640625" style="5" customWidth="1"/>
-    <col min="16" max="17" width="10.83203125" style="5"/>
-    <col min="18" max="18" width="73" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="10.83203125" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="59" t="s">
-        <v>296</v>
-      </c>
-      <c r="B2" s="59" t="s">
-        <v>225</v>
-      </c>
-      <c r="C2" s="59" t="s">
-        <v>226</v>
-      </c>
-      <c r="D2" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="E2" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="F2" s="59" t="s">
-        <v>229</v>
-      </c>
-      <c r="G2" s="60" t="s">
-        <v>230</v>
-      </c>
-      <c r="H2" s="59" t="s">
-        <v>297</v>
-      </c>
-      <c r="I2" s="60"/>
-      <c r="J2" s="59" t="s">
-        <v>298</v>
-      </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="59" t="s">
-        <v>299</v>
-      </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="3" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" s="5" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="59"/>
-      <c r="B3" s="59"/>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="59"/>
-      <c r="G3" s="60"/>
-      <c r="H3" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>302</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="M3" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="N3" s="41" t="s">
-        <v>306</v>
-      </c>
-      <c r="O3" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="P3" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q3" s="39" t="s">
-        <v>310</v>
-      </c>
-      <c r="R3" s="40" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="37" t="s">
-        <v>212</v>
-      </c>
-      <c r="B4" s="37"/>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
-      <c r="F4" s="37"/>
-      <c r="G4" s="37"/>
-      <c r="H4" s="37"/>
-      <c r="I4" s="37"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
-      <c r="L4" s="43"/>
-      <c r="M4" s="43"/>
-      <c r="N4" s="43"/>
-      <c r="O4" s="43"/>
-      <c r="P4" s="43"/>
-      <c r="Q4" s="43"/>
-      <c r="R4" s="37"/>
-    </row>
-    <row r="5" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>225243415</v>
-      </c>
-      <c r="E5" s="1">
-        <v>225266802</v>
-      </c>
-      <c r="F5" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H5" s="46">
-        <v>1.9569000000000001</v>
-      </c>
-      <c r="I5" s="44">
-        <v>2.5179E-2</v>
-      </c>
-      <c r="J5" s="5">
-        <v>6</v>
-      </c>
-      <c r="K5" s="5">
-        <v>7.548</v>
-      </c>
-      <c r="L5" s="7">
-        <v>7.9629999999999897E-6</v>
-      </c>
-      <c r="M5" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="N5" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O5" s="5">
-        <v>193</v>
-      </c>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="50"/>
-      <c r="R5" s="38" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>237</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>225334867</v>
-      </c>
-      <c r="E6" s="1">
-        <v>225450110</v>
-      </c>
-      <c r="F6" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H6" s="46">
-        <v>3.9108000000000001</v>
-      </c>
-      <c r="I6" s="44">
-        <v>4.5989000000000003E-5</v>
-      </c>
-      <c r="J6" s="5">
-        <v>170</v>
-      </c>
-      <c r="K6" s="5">
-        <v>22.4</v>
-      </c>
-      <c r="L6" s="7">
-        <v>7.9629999999999897E-6</v>
-      </c>
-      <c r="M6" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="N6" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O6" s="5">
-        <v>189</v>
-      </c>
-      <c r="P6" s="7"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="38" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>225364104</v>
-      </c>
-      <c r="E7" s="1">
-        <v>225364817</v>
-      </c>
-      <c r="F7" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="H7" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I7" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J7" s="5">
-        <v>30</v>
-      </c>
-      <c r="K7" s="5">
-        <v>22.4</v>
-      </c>
-      <c r="L7" s="7">
-        <v>7.9629999999999897E-6</v>
-      </c>
-      <c r="M7" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="N7" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O7" s="5">
-        <v>209</v>
-      </c>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="38" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C8" s="1">
-        <v>7</v>
-      </c>
-      <c r="D8" s="1">
-        <v>157128075</v>
-      </c>
-      <c r="E8" s="1">
-        <v>157210133</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H8" s="46">
-        <v>4.1135000000000002</v>
-      </c>
-      <c r="I8" s="44">
-        <v>1.9483999999999998E-5</v>
-      </c>
-      <c r="J8" s="5">
-        <v>99</v>
-      </c>
-      <c r="K8" s="5">
-        <v>9.0809999999999995</v>
-      </c>
-      <c r="L8" s="7">
-        <v>4.6600000000000003E-6</v>
-      </c>
-      <c r="M8" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="N8" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O8" s="5">
-        <v>98</v>
-      </c>
-      <c r="P8" s="7"/>
-      <c r="Q8" s="39"/>
-      <c r="R8" s="38" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>248</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>249</v>
-      </c>
-      <c r="C9" s="1">
-        <v>11</v>
-      </c>
-      <c r="D9" s="1">
-        <v>77225981</v>
-      </c>
-      <c r="E9" s="1">
-        <v>77348850</v>
-      </c>
-      <c r="F9" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H9" s="46">
-        <v>1.8856999999999999</v>
-      </c>
-      <c r="I9" s="44">
-        <v>2.9666999999999999E-2</v>
-      </c>
-      <c r="J9" s="5">
-        <v>2</v>
-      </c>
-      <c r="K9" s="5">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="L9" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M9" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N9" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O9" s="5">
-        <v>36</v>
-      </c>
-      <c r="P9" s="7"/>
-      <c r="Q9" s="44"/>
-      <c r="R9" s="38" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C10" s="1">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1">
-        <v>77300436</v>
-      </c>
-      <c r="E10" s="1">
-        <v>77321400</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I10" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J10" s="5">
-        <v>1</v>
-      </c>
-      <c r="K10" s="5">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="L10" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M10" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N10" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O10" s="5">
-        <v>62</v>
-      </c>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="39"/>
-      <c r="R10" s="38" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="C11" s="1">
-        <v>11</v>
-      </c>
-      <c r="D11" s="1">
-        <v>77428757</v>
-      </c>
-      <c r="E11" s="1">
-        <v>77429456</v>
-      </c>
-      <c r="F11" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>258</v>
-      </c>
-      <c r="H11" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I11" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J11" s="5">
-        <v>2</v>
-      </c>
-      <c r="K11" s="5">
-        <v>11.5</v>
-      </c>
-      <c r="L11" s="7">
-        <v>3.1649999999999902E-5</v>
-      </c>
-      <c r="M11" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N11" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O11" s="5">
-        <v>2</v>
-      </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="44"/>
-      <c r="R11" s="38" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="1">
-        <v>11</v>
-      </c>
-      <c r="D12" s="1">
-        <v>77532155</v>
-      </c>
-      <c r="E12" s="1">
-        <v>77629478</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H12" s="46">
-        <v>3.181</v>
-      </c>
-      <c r="I12" s="44">
-        <v>7.3379999999999995E-4</v>
-      </c>
-      <c r="J12" s="5">
-        <v>33</v>
-      </c>
-      <c r="K12" s="5">
-        <v>14.98</v>
-      </c>
-      <c r="L12" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M12" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N12" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O12" s="5">
-        <v>65</v>
-      </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="44"/>
-      <c r="R12" s="38" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>261</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>262</v>
-      </c>
-      <c r="C13" s="1">
-        <v>11</v>
-      </c>
-      <c r="D13" s="1">
-        <v>77540700</v>
-      </c>
-      <c r="E13" s="1">
-        <v>77583308</v>
-      </c>
-      <c r="F13" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G13" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H13" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I13" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J13" s="5">
-        <v>24</v>
-      </c>
-      <c r="K13" s="5">
-        <v>12.9</v>
-      </c>
-      <c r="L13" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M13" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N13" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O13" s="5">
-        <v>60</v>
-      </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="44"/>
-      <c r="R13" s="38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>265</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C14" s="1">
-        <v>11</v>
-      </c>
-      <c r="D14" s="1">
-        <v>77561650</v>
-      </c>
-      <c r="E14" s="1">
-        <v>77562557</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H14" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I14" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J14" s="5">
-        <v>7</v>
-      </c>
-      <c r="K14" s="5">
-        <v>9.8940000000000001</v>
-      </c>
-      <c r="L14" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M14" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N14" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O14" s="5">
-        <v>60</v>
-      </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="39"/>
-      <c r="R14" s="38" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>268</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>269</v>
-      </c>
-      <c r="C15" s="1">
-        <v>11</v>
-      </c>
-      <c r="D15" s="1">
-        <v>77577458</v>
-      </c>
-      <c r="E15" s="1">
-        <v>77581137</v>
-      </c>
-      <c r="F15" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H15" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I15" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J15" s="5">
-        <v>12</v>
-      </c>
-      <c r="K15" s="5">
-        <v>12.9</v>
-      </c>
-      <c r="L15" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M15" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N15" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O15" s="5">
-        <v>41</v>
-      </c>
-      <c r="P15" s="7"/>
-      <c r="Q15" s="44"/>
-      <c r="R15" s="38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>271</v>
-      </c>
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>77579768</v>
-      </c>
-      <c r="E16" s="1">
-        <v>77580241</v>
-      </c>
-      <c r="F16" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="H16" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I16" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J16" s="5">
-        <v>10</v>
-      </c>
-      <c r="K16" s="5">
-        <v>12.9</v>
-      </c>
-      <c r="L16" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M16" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N16" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O16" s="5">
-        <v>59</v>
-      </c>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="39"/>
-      <c r="R16" s="38" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="C17" s="1">
-        <v>11</v>
-      </c>
-      <c r="D17" s="1">
-        <v>77589766</v>
-      </c>
-      <c r="E17" s="1">
-        <v>77705724</v>
-      </c>
-      <c r="F17" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G17" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H17" s="46">
-        <v>2.1533000000000002</v>
-      </c>
-      <c r="I17" s="44">
-        <v>1.5649E-2</v>
-      </c>
-      <c r="J17" s="5">
-        <v>13</v>
-      </c>
-      <c r="K17" s="5">
-        <v>14.98</v>
-      </c>
-      <c r="L17" s="7">
-        <v>5.1189999999999903E-6</v>
-      </c>
-      <c r="M17" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="N17" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O17" s="5">
-        <v>66</v>
-      </c>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="51"/>
-      <c r="R17" s="38" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37" t="s">
-        <v>214</v>
-      </c>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="47"/>
-      <c r="I18" s="45"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="49"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="37"/>
-    </row>
-    <row r="19" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>276</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="C19" s="1">
-        <v>10</v>
-      </c>
-      <c r="D19" s="1">
-        <v>23556124</v>
-      </c>
-      <c r="E19" s="1">
-        <v>23633774</v>
-      </c>
-      <c r="F19" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H19" s="46">
-        <v>3.8144999999999998</v>
-      </c>
-      <c r="I19" s="44">
-        <v>6.8224000000000003E-5</v>
-      </c>
-      <c r="J19" s="5">
-        <v>31</v>
-      </c>
-      <c r="K19" s="5">
-        <v>5.6379999999999999</v>
-      </c>
-      <c r="L19" s="7">
-        <v>1.5200000000000001E-6</v>
-      </c>
-      <c r="M19" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="N19" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O19" s="5">
-        <v>59</v>
-      </c>
-      <c r="P19" s="7"/>
-      <c r="Q19" s="44"/>
-      <c r="R19" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>278</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C20" s="1">
-        <v>10</v>
-      </c>
-      <c r="D20" s="1">
-        <v>23632886</v>
-      </c>
-      <c r="E20" s="1">
-        <v>23634110</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>263</v>
-      </c>
-      <c r="H20" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="I20" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="J20" s="5">
-        <v>20</v>
-      </c>
-      <c r="K20" s="5">
-        <v>5.6379999999999999</v>
-      </c>
-      <c r="L20" s="7">
-        <v>3.18E-6</v>
-      </c>
-      <c r="M20" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="N20" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O20" s="5">
-        <v>57</v>
-      </c>
-      <c r="P20" s="7"/>
-      <c r="Q20" s="52"/>
-      <c r="R20" s="5" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="21" spans="1:18" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="37" t="s">
-        <v>295</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="47"/>
-      <c r="I21" s="45"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="43"/>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="49"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="37"/>
-    </row>
-    <row r="22" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C22" s="1">
-        <v>4</v>
-      </c>
-      <c r="D22" s="1">
-        <v>114372188</v>
-      </c>
-      <c r="E22" s="1">
-        <v>114683083</v>
-      </c>
-      <c r="F22" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H22" s="48">
-        <v>0.83581000000000005</v>
-      </c>
-      <c r="I22" s="44">
-        <v>0.20163</v>
-      </c>
-      <c r="K22" s="5">
-        <v>6.6879999999999997</v>
-      </c>
-      <c r="L22" s="7">
-        <v>6.7939999999999903E-6</v>
-      </c>
-      <c r="M22" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="N22" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O22" s="5">
-        <v>17</v>
-      </c>
-      <c r="P22" s="7"/>
-      <c r="Q22" s="50"/>
-      <c r="R22" s="1" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="23" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="1" t="s">
-        <v>283</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="C23" s="1">
-        <v>6</v>
-      </c>
-      <c r="D23" s="1">
-        <v>64429876</v>
-      </c>
-      <c r="E23" s="1">
-        <v>66417118</v>
-      </c>
-      <c r="F23" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H23" s="46">
-        <v>4.4518000000000004</v>
-      </c>
-      <c r="I23" s="44">
-        <v>4.2579999999999997E-6</v>
-      </c>
-      <c r="J23" s="5">
-        <v>248</v>
-      </c>
-      <c r="K23" s="5">
-        <v>14.04</v>
-      </c>
-      <c r="L23" s="7">
-        <v>8.6160000000000002E-6</v>
-      </c>
-      <c r="M23" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="N23" s="41" t="s">
-        <v>238</v>
-      </c>
-      <c r="O23" s="5">
-        <v>218</v>
-      </c>
-      <c r="P23" s="7"/>
-      <c r="Q23" s="44"/>
-      <c r="R23" s="1" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>288</v>
-      </c>
-      <c r="C24" s="1">
-        <v>8</v>
-      </c>
-      <c r="D24" s="1">
-        <v>19261672</v>
-      </c>
-      <c r="E24" s="1">
-        <v>19615540</v>
-      </c>
-      <c r="F24" s="1">
-        <v>-1</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H24" s="46">
-        <v>4.1064999999999996</v>
-      </c>
-      <c r="I24" s="44">
-        <v>2.0085000000000002E-5</v>
-      </c>
-      <c r="J24" s="5">
-        <v>103</v>
-      </c>
-      <c r="K24" s="5">
-        <v>13.07</v>
-      </c>
-      <c r="L24" s="7">
-        <v>7.5719999999999904E-6</v>
-      </c>
-      <c r="M24" s="39" t="s">
-        <v>290</v>
-      </c>
-      <c r="N24" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O24" s="5">
-        <v>79</v>
-      </c>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="39"/>
-      <c r="R24" s="1" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="C25" s="1">
-        <v>15</v>
-      </c>
-      <c r="D25" s="1">
-        <v>59157374</v>
-      </c>
-      <c r="E25" s="1">
-        <v>59389618</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>305</v>
-      </c>
-      <c r="H25" s="46">
-        <v>3.1720000000000002</v>
-      </c>
-      <c r="I25" s="44">
-        <v>7.5688000000000003E-4</v>
-      </c>
-      <c r="J25" s="5">
-        <v>20</v>
-      </c>
-      <c r="K25" s="5">
-        <v>7.6980000000000004</v>
-      </c>
-      <c r="L25" s="7">
-        <v>8.4789999999999895E-6</v>
-      </c>
-      <c r="M25" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="N25" s="41" t="s">
-        <v>307</v>
-      </c>
-      <c r="O25" s="5">
-        <v>2</v>
-      </c>
-      <c r="P25" s="7"/>
-      <c r="Q25" s="39"/>
-      <c r="R25" s="1" t="s">
-        <v>293</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C2:C3"/>
-    <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="N2:Q2"/>
-  </mergeCells>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB28FFE0-8F36-1743-BBFF-32F0871E000C}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -3634,7 +2076,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C1" s="12"/>
       <c r="D1" s="12"/>
@@ -3650,38 +2092,38 @@
       <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="47" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="69" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="51" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="64"/>
-      <c r="E2" s="64" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="70"/>
-      <c r="G2" s="69" t="s">
+      <c r="F2" s="52"/>
+      <c r="G2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64" t="s">
+      <c r="H2" s="46"/>
+      <c r="I2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="70"/>
-      <c r="K2" s="69" t="s">
+      <c r="J2" s="52"/>
+      <c r="K2" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64" t="s">
+      <c r="L2" s="46"/>
+      <c r="M2" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="64"/>
+      <c r="N2" s="46"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="67"/>
-      <c r="B3" s="68"/>
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
@@ -3721,26 +2163,26 @@
       <c r="O3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="63"/>
-      <c r="J4" s="63"/>
-      <c r="K4" s="63"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="63"/>
-      <c r="N4" s="63"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
       <c r="O4" s="26"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="61" t="s">
+      <c r="A5" s="42" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="22" t="s">
@@ -3783,10 +2225,10 @@
         <v>0.38106893052840601</v>
       </c>
       <c r="O5" s="26"/>
-      <c r="P5" s="53"/>
+      <c r="P5" s="36"/>
     </row>
     <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="59"/>
+      <c r="A6" s="43"/>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
@@ -3827,10 +2269,10 @@
         <v>1.15793313475917E-2</v>
       </c>
       <c r="O6" s="26"/>
-      <c r="P6" s="53"/>
+      <c r="P6" s="36"/>
     </row>
     <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="59"/>
+      <c r="A7" s="43"/>
       <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
@@ -3871,10 +2313,10 @@
         <v>135</v>
       </c>
       <c r="O7" s="26"/>
-      <c r="P7" s="53"/>
+      <c r="P7" s="36"/>
     </row>
     <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="59"/>
+      <c r="A8" s="43"/>
       <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
@@ -3915,10 +2357,10 @@
         <v>0.42471750538549602</v>
       </c>
       <c r="O8" s="26"/>
-      <c r="P8" s="53"/>
+      <c r="P8" s="36"/>
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="59"/>
+      <c r="A9" s="43"/>
       <c r="B9" s="23" t="s">
         <v>12</v>
       </c>
@@ -3959,10 +2401,10 @@
         <v>0.39740315206358801</v>
       </c>
       <c r="O9" s="26"/>
-      <c r="P9" s="53"/>
+      <c r="P9" s="36"/>
     </row>
     <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="43" t="s">
         <v>215</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -4005,10 +2447,10 @@
         <v>5.8407805811169999E-2</v>
       </c>
       <c r="O10" s="26"/>
-      <c r="P10" s="53"/>
+      <c r="P10" s="36"/>
     </row>
     <row r="11" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="59"/>
+      <c r="A11" s="43"/>
       <c r="B11" s="23" t="s">
         <v>9</v>
       </c>
@@ -4049,10 +2491,10 @@
         <v>7.9525598884296906E-3</v>
       </c>
       <c r="O11" s="26"/>
-      <c r="P11" s="53"/>
+      <c r="P11" s="36"/>
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="59"/>
+      <c r="A12" s="43"/>
       <c r="B12" s="23" t="s">
         <v>10</v>
       </c>
@@ -4093,10 +2535,10 @@
         <v>5.3799840360692598E-5</v>
       </c>
       <c r="O12" s="26"/>
-      <c r="P12" s="53"/>
+      <c r="P12" s="36"/>
     </row>
     <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="59"/>
+      <c r="A13" s="43"/>
       <c r="B13" s="23" t="s">
         <v>11</v>
       </c>
@@ -4137,10 +2579,10 @@
         <v>0.167336762598818</v>
       </c>
       <c r="O13" s="26"/>
-      <c r="P13" s="53"/>
+      <c r="P13" s="36"/>
     </row>
     <row r="14" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62"/>
+      <c r="A14" s="44"/>
       <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
@@ -4181,30 +2623,30 @@
         <v>0.159973818673354</v>
       </c>
       <c r="O14" s="26"/>
-      <c r="P14" s="53"/>
+      <c r="P14" s="36"/>
     </row>
     <row r="15" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="63" t="s">
+      <c r="A15" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="63"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="63"/>
-      <c r="I15" s="63"/>
-      <c r="J15" s="63"/>
-      <c r="K15" s="63"/>
-      <c r="L15" s="63"/>
-      <c r="M15" s="63"/>
-      <c r="N15" s="63"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
+      <c r="J15" s="45"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="45"/>
+      <c r="M15" s="45"/>
+      <c r="N15" s="45"/>
       <c r="O15" s="26"/>
-      <c r="P15" s="53"/>
+      <c r="P15" s="36"/>
     </row>
     <row r="16" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="61" t="s">
+      <c r="A16" s="42" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="22" t="s">
@@ -4247,10 +2689,10 @@
         <v>0.37890405517586201</v>
       </c>
       <c r="O16" s="26"/>
-      <c r="P16" s="53"/>
+      <c r="P16" s="36"/>
     </row>
     <row r="17" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="59"/>
+      <c r="A17" s="43"/>
       <c r="B17" s="23" t="s">
         <v>9</v>
       </c>
@@ -4291,10 +2733,10 @@
         <v>1.3166532350849299E-2</v>
       </c>
       <c r="O17" s="26"/>
-      <c r="P17" s="53"/>
+      <c r="P17" s="36"/>
     </row>
     <row r="18" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="59"/>
+      <c r="A18" s="43"/>
       <c r="B18" s="23" t="s">
         <v>10</v>
       </c>
@@ -4335,10 +2777,10 @@
         <v>135</v>
       </c>
       <c r="O18" s="26"/>
-      <c r="P18" s="53"/>
+      <c r="P18" s="36"/>
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="59"/>
+      <c r="A19" s="43"/>
       <c r="B19" s="23" t="s">
         <v>11</v>
       </c>
@@ -4379,10 +2821,10 @@
         <v>0.39340512922514598</v>
       </c>
       <c r="O19" s="26"/>
-      <c r="P19" s="53"/>
+      <c r="P19" s="36"/>
     </row>
     <row r="20" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="59"/>
+      <c r="A20" s="43"/>
       <c r="B20" s="23" t="s">
         <v>12</v>
       </c>
@@ -4423,10 +2865,10 @@
         <v>0.35337022863699302</v>
       </c>
       <c r="O20" s="26"/>
-      <c r="P20" s="53"/>
+      <c r="P20" s="36"/>
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="59" t="s">
+      <c r="A21" s="43" t="s">
         <v>215</v>
       </c>
       <c r="B21" s="23" t="s">
@@ -4469,10 +2911,10 @@
         <v>0.11913339381211201</v>
       </c>
       <c r="O21" s="26"/>
-      <c r="P21" s="53"/>
+      <c r="P21" s="36"/>
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="59"/>
+      <c r="A22" s="43"/>
       <c r="B22" s="23" t="s">
         <v>9</v>
       </c>
@@ -4513,10 +2955,10 @@
         <v>1.1056362777466E-2</v>
       </c>
       <c r="O22" s="26"/>
-      <c r="P22" s="53"/>
+      <c r="P22" s="36"/>
     </row>
     <row r="23" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="59"/>
+      <c r="A23" s="43"/>
       <c r="B23" s="23" t="s">
         <v>10</v>
       </c>
@@ -4557,10 +2999,10 @@
         <v>5.8679478272561096E-4</v>
       </c>
       <c r="O23" s="26"/>
-      <c r="P23" s="53"/>
+      <c r="P23" s="36"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="59"/>
+      <c r="A24" s="43"/>
       <c r="B24" s="23" t="s">
         <v>11</v>
       </c>
@@ -4600,10 +3042,10 @@
       <c r="N24" s="8">
         <v>0.102270857663914</v>
       </c>
-      <c r="P24" s="53"/>
+      <c r="P24" s="36"/>
     </row>
     <row r="25" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="62"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="24" t="s">
         <v>12</v>
       </c>
@@ -4643,29 +3085,29 @@
       <c r="N25" s="8">
         <v>9.9620575405391196E-2</v>
       </c>
-      <c r="P25" s="53"/>
+      <c r="P25" s="36"/>
     </row>
     <row r="26" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="63" t="s">
+      <c r="A26" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="63"/>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
-      <c r="F26" s="63"/>
-      <c r="G26" s="63"/>
-      <c r="H26" s="63"/>
-      <c r="I26" s="63"/>
-      <c r="J26" s="63"/>
-      <c r="K26" s="63"/>
-      <c r="L26" s="63"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="63"/>
-      <c r="P26" s="53"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="45"/>
+      <c r="P26" s="36"/>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="61" t="s">
+      <c r="A27" s="42" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="22" t="s">
@@ -4707,10 +3149,10 @@
       <c r="N27" s="8">
         <v>0.38106893052840601</v>
       </c>
-      <c r="P27" s="53"/>
+      <c r="P27" s="36"/>
     </row>
     <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="59"/>
+      <c r="A28" s="43"/>
       <c r="B28" s="23" t="s">
         <v>9</v>
       </c>
@@ -4750,10 +3192,10 @@
       <c r="N28" s="8">
         <v>1.44882589075758E-2</v>
       </c>
-      <c r="P28" s="53"/>
+      <c r="P28" s="36"/>
     </row>
     <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="59"/>
+      <c r="A29" s="43"/>
       <c r="B29" s="23" t="s">
         <v>10</v>
       </c>
@@ -4793,10 +3235,10 @@
       <c r="N29" s="34" t="s">
         <v>135</v>
       </c>
-      <c r="P29" s="53"/>
+      <c r="P29" s="36"/>
     </row>
     <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="59"/>
+      <c r="A30" s="43"/>
       <c r="B30" s="23" t="s">
         <v>11</v>
       </c>
@@ -4836,10 +3278,10 @@
       <c r="N30" s="8">
         <v>0.35601381888108602</v>
       </c>
-      <c r="P30" s="53"/>
+      <c r="P30" s="36"/>
     </row>
     <row r="31" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="59"/>
+      <c r="A31" s="43"/>
       <c r="B31" s="23" t="s">
         <v>12</v>
       </c>
@@ -4879,10 +3321,10 @@
       <c r="N31" s="8">
         <v>0.40157310797477302</v>
       </c>
-      <c r="P31" s="53"/>
+      <c r="P31" s="36"/>
     </row>
     <row r="32" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="59" t="s">
+      <c r="A32" s="43" t="s">
         <v>215</v>
       </c>
       <c r="B32" s="23" t="s">
@@ -4924,10 +3366,10 @@
       <c r="N32" s="8">
         <v>5.8407805811169999E-2</v>
       </c>
-      <c r="P32" s="53"/>
+      <c r="P32" s="36"/>
     </row>
     <row r="33" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="59"/>
+      <c r="A33" s="43"/>
       <c r="B33" s="23" t="s">
         <v>9</v>
       </c>
@@ -4967,10 +3409,10 @@
       <c r="N33" s="8">
         <v>7.6306339845722496E-3</v>
       </c>
-      <c r="P33" s="53"/>
+      <c r="P33" s="36"/>
     </row>
     <row r="34" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="59"/>
+      <c r="A34" s="43"/>
       <c r="B34" s="23" t="s">
         <v>10</v>
       </c>
@@ -5010,10 +3452,10 @@
       <c r="N34" s="8">
         <v>5.3799840360692598E-5</v>
       </c>
-      <c r="P34" s="53"/>
+      <c r="P34" s="36"/>
     </row>
     <row r="35" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="59"/>
+      <c r="A35" s="43"/>
       <c r="B35" s="23" t="s">
         <v>11</v>
       </c>
@@ -5053,10 +3495,10 @@
       <c r="N35" s="8">
         <v>0.18536224528602299</v>
       </c>
-      <c r="P35" s="53"/>
+      <c r="P35" s="36"/>
     </row>
     <row r="36" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="62"/>
+      <c r="A36" s="44"/>
       <c r="B36" s="24" t="s">
         <v>12</v>
       </c>
@@ -5096,7 +3538,7 @@
       <c r="N36" s="14">
         <v>0.17157671655635501</v>
       </c>
-      <c r="P36" s="53"/>
+      <c r="P36" s="36"/>
     </row>
     <row r="37" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F37" s="5"/>

--- a/table/Tables.xlsx
+++ b/table/Tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/annabethlu/Projects/ded-dep-ibs/table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DA77450-140E-CA40-AF03-E45B3F95ADF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C793B63-2B8D-3D44-84C9-C84F643E7705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="920" yWindow="760" windowWidth="28480" windowHeight="18360" activeTab="1" xr2:uid="{D515C405-0CB0-4046-88E1-6357459E1EB7}"/>
+    <workbookView xWindow="980" yWindow="660" windowWidth="28420" windowHeight="18460" activeTab="2" xr2:uid="{D515C405-0CB0-4046-88E1-6357459E1EB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Table of content" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="313">
   <si>
     <t>Genome-wide Association Study (GWAS)</t>
   </si>
@@ -809,6 +809,255 @@
   <si>
     <t>13.59% (620)</t>
   </si>
+  <si>
+    <t>Table 2. Genes Prioritized by Positional, eQTL and Chromatin Interaction Mappings</t>
+  </si>
+  <si>
+    <t>rsID</t>
+  </si>
+  <si>
+    <t>chr</t>
+  </si>
+  <si>
+    <t>pos</t>
+  </si>
+  <si>
+    <t>rs12044984</t>
+  </si>
+  <si>
+    <t>rs4624371</t>
+  </si>
+  <si>
+    <t>rs66799507</t>
+  </si>
+  <si>
+    <t>rs6431289</t>
+  </si>
+  <si>
+    <t>rs1872982</t>
+  </si>
+  <si>
+    <t>rs4863709</t>
+  </si>
+  <si>
+    <t>rs17314832</t>
+  </si>
+  <si>
+    <t>rs147187651</t>
+  </si>
+  <si>
+    <t>rs2187437</t>
+  </si>
+  <si>
+    <t>rs147090214</t>
+  </si>
+  <si>
+    <t>rs9692250</t>
+  </si>
+  <si>
+    <t>rs4468275</t>
+  </si>
+  <si>
+    <t>rs9333182</t>
+  </si>
+  <si>
+    <t>rs687037</t>
+  </si>
+  <si>
+    <t>rs10438549</t>
+  </si>
+  <si>
+    <t>non_effect_allele</t>
+  </si>
+  <si>
+    <t>effect_allele</t>
+  </si>
+  <si>
+    <t>MAF</t>
+  </si>
+  <si>
+    <t>gwasP</t>
+  </si>
+  <si>
+    <t>r2</t>
+  </si>
+  <si>
+    <t>IndSigSNP</t>
+  </si>
+  <si>
+    <t>GenomicLocus</t>
+  </si>
+  <si>
+    <t>nearestGene</t>
+  </si>
+  <si>
+    <t>dist</t>
+  </si>
+  <si>
+    <t>func</t>
+  </si>
+  <si>
+    <t>CADD</t>
+  </si>
+  <si>
+    <t>RDB</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>RNU4-28P</t>
+  </si>
+  <si>
+    <t>intergenic</t>
+  </si>
+  <si>
+    <t>CUL3</t>
+  </si>
+  <si>
+    <t>AC010148.1</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C3orf55</t>
+  </si>
+  <si>
+    <t>MAML3</t>
+  </si>
+  <si>
+    <t>intronic</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>ECT2L</t>
+  </si>
+  <si>
+    <t>RP11-307P5.1</t>
+  </si>
+  <si>
+    <t>ncRNA_intronic</t>
+  </si>
+  <si>
+    <t>TCTTA</t>
+  </si>
+  <si>
+    <t>AC015987.1</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>DNAJB6</t>
+  </si>
+  <si>
+    <t>exonic</t>
+  </si>
+  <si>
+    <t>LINC00701</t>
+  </si>
+  <si>
+    <t>ITGA8</t>
+  </si>
+  <si>
+    <t>AAMDC:INTS4</t>
+  </si>
+  <si>
+    <t>RP11-354I13.1</t>
+  </si>
+  <si>
+    <t>OR</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>rs927751</t>
+  </si>
+  <si>
+    <t>C10orf115</t>
+  </si>
+  <si>
+    <t>rs71714702</t>
+  </si>
+  <si>
+    <t>GAGCATTGCTTTCTTATCTGAACCTCTA</t>
+  </si>
+  <si>
+    <t>RGS7</t>
+  </si>
+  <si>
+    <t>rs4072527</t>
+  </si>
+  <si>
+    <t>AC096649.3</t>
+  </si>
+  <si>
+    <t>rs62177211</t>
+  </si>
+  <si>
+    <t>OSBPL6</t>
+  </si>
+  <si>
+    <t>rs2040744</t>
+  </si>
+  <si>
+    <t>CAMK2D</t>
+  </si>
+  <si>
+    <t>rs12663968</t>
+  </si>
+  <si>
+    <t>EYS</t>
+  </si>
+  <si>
+    <t>rs146409271</t>
+  </si>
+  <si>
+    <t>SEC63</t>
+  </si>
+  <si>
+    <t>rs4332151</t>
+  </si>
+  <si>
+    <t>CSGALNACT1</t>
+  </si>
+  <si>
+    <t>rs55829750</t>
+  </si>
+  <si>
+    <t>AMD1P1</t>
+  </si>
+  <si>
+    <t>rs34868598</t>
+  </si>
+  <si>
+    <t>RNF111</t>
+  </si>
+  <si>
+    <t>downstream</t>
+  </si>
+  <si>
+    <t>rs78845406</t>
+  </si>
+  <si>
+    <t>PTPRM</t>
+  </si>
+  <si>
+    <t>rs35484580</t>
+  </si>
+  <si>
+    <t>CTB-32O4.2</t>
+  </si>
+  <si>
+    <t>Irritable bowel syndrome</t>
+  </si>
 </sst>
 </file>
 
@@ -818,7 +1067,7 @@
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -900,6 +1149,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -909,7 +1164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -1012,6 +1267,46 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1019,7 +1314,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1129,53 +1424,83 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1554,7 +1879,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E90501A7-715E-F04D-8391-BB22BC15A0D4}">
   <sheetPr codeName="Sheet4"/>
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.83203125" style="3" customWidth="1"/>
@@ -1581,23 +1906,23 @@
       <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="61" t="s">
         <v>212</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="60" t="s">
         <v>197</v>
       </c>
-      <c r="C2" s="37"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="37" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="E2" s="60" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="37"/>
-      <c r="G2" s="37"/>
+      <c r="F2" s="60"/>
+      <c r="G2" s="60"/>
       <c r="I2" s="4"/>
     </row>
     <row r="3" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="41"/>
+      <c r="A3" s="62"/>
       <c r="B3" s="31" t="s">
         <v>228</v>
       </c>
@@ -1699,23 +2024,23 @@
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="58" t="s">
         <v>214</v>
       </c>
-      <c r="B8" s="37" t="s">
+      <c r="B8" s="60" t="s">
         <v>210</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37" t="s">
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60" t="s">
         <v>184</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
+      <c r="F8" s="60"/>
+      <c r="G8" s="60"/>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="39"/>
+      <c r="A9" s="59"/>
       <c r="B9" s="31" t="s">
         <v>185</v>
       </c>
@@ -1821,23 +2146,23 @@
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="58" t="s">
         <v>211</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="60" t="s">
         <v>168</v>
       </c>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37" t="s">
+      <c r="C14" s="60"/>
+      <c r="D14" s="60"/>
+      <c r="E14" s="60" t="s">
         <v>169</v>
       </c>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
+      <c r="F14" s="60"/>
+      <c r="G14" s="60"/>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="39"/>
+      <c r="A15" s="59"/>
       <c r="B15" s="31" t="s">
         <v>170</v>
       </c>
@@ -2017,25 +2342,16 @@
     <row r="44" spans="9:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="9:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="9:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="9:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="I47" s="4"/>
-    </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="E2:G2"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E14:G14"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A8:A9"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="E8:G8"/>
-    <mergeCell ref="E14:G14"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="E2:G2"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2045,9 +2361,1745 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB28FFE0-8F36-1743-BBFF-32F0871E000C}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:Q48"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.83203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.83203125" style="3"/>
+    <col min="12" max="12" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.83203125" style="3"/>
+    <col min="14" max="14" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.83203125" style="3"/>
+    <col min="16" max="17" width="11" style="3" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="10.83203125" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
+      <c r="M1" s="39"/>
+      <c r="N1" s="39"/>
+      <c r="O1" s="39"/>
+      <c r="P1" s="39"/>
+      <c r="Q1" s="39"/>
+    </row>
+    <row r="2" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="38" t="s">
+        <v>212</v>
+      </c>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
+      <c r="K2" s="39"/>
+      <c r="L2" s="39"/>
+      <c r="M2" s="39"/>
+      <c r="N2" s="39"/>
+      <c r="O2" s="39"/>
+      <c r="P2" s="39"/>
+      <c r="Q2" s="39"/>
+    </row>
+    <row r="3" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>232</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E3" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="G3" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="J3" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="L3" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="M3" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="N3" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="O3" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="P3" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q3" s="37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" s="41">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5">
+        <v>19841504</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.42459999999999998</v>
+      </c>
+      <c r="G4" s="5">
+        <v>4.3900000000000003E-6</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.9163</v>
+      </c>
+      <c r="I4" s="5">
+        <v>1.9040000000000001E-2</v>
+      </c>
+      <c r="J4" s="5">
+        <v>1</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="L4" s="5">
+        <v>1</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="N4" s="5">
+        <v>4276</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P4" s="5">
+        <v>2.5950000000000002</v>
+      </c>
+      <c r="Q4" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="5">
+        <v>2</v>
+      </c>
+      <c r="C5" s="5">
+        <v>225466404</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.247</v>
+      </c>
+      <c r="G5" s="5">
+        <v>7.96E-6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>1.101</v>
+      </c>
+      <c r="I5" s="5">
+        <v>2.1499999999999998E-2</v>
+      </c>
+      <c r="J5" s="5">
+        <v>1</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="L5" s="5">
+        <v>2</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="N5" s="5">
+        <v>16293</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P5" s="5">
+        <v>12.89</v>
+      </c>
+      <c r="Q5" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5">
+        <v>235637935</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F6" s="5">
+        <v>9.1270000000000004E-2</v>
+      </c>
+      <c r="G6" s="5">
+        <v>3.4999999999999999E-6</v>
+      </c>
+      <c r="H6" s="5">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="I6" s="5">
+        <v>2.8340000000000001E-2</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L6" s="5">
+        <v>3</v>
+      </c>
+      <c r="M6" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="N6" s="5">
+        <v>105023</v>
+      </c>
+      <c r="O6" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P6" s="5">
+        <v>1.228</v>
+      </c>
+      <c r="Q6" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="B7" s="5">
+        <v>2</v>
+      </c>
+      <c r="C7" s="5">
+        <v>235659340</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" s="5">
+        <v>5.4559999999999997E-2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3.9099999999999998E-6</v>
+      </c>
+      <c r="H7" s="5">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="I7" s="5">
+        <v>3.363E-2</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="L7" s="5">
+        <v>3</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>266</v>
+      </c>
+      <c r="N7" s="5">
+        <v>83618</v>
+      </c>
+      <c r="O7" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P7" s="5">
+        <v>3.9049999999999998</v>
+      </c>
+      <c r="Q7" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="B8" s="5">
+        <v>3</v>
+      </c>
+      <c r="C8" s="5">
+        <v>157498846</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.23019999999999999</v>
+      </c>
+      <c r="G8" s="5">
+        <v>6.1600000000000003E-6</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.90080000000000005</v>
+      </c>
+      <c r="I8" s="5">
+        <v>2.3109999999999999E-2</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="L8" s="5">
+        <v>4</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="N8" s="5">
+        <v>103307</v>
+      </c>
+      <c r="O8" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P8" s="5">
+        <v>1.766</v>
+      </c>
+      <c r="Q8" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="B9" s="5">
+        <v>4</v>
+      </c>
+      <c r="C9" s="5">
+        <v>140891233</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.4365</v>
+      </c>
+      <c r="G9" s="5">
+        <v>5.7799999999999997E-6</v>
+      </c>
+      <c r="H9" s="5">
+        <v>1.093</v>
+      </c>
+      <c r="I9" s="5">
+        <v>1.9539999999999998E-2</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="L9" s="5">
+        <v>5</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="N9" s="5">
+        <v>0</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P9" s="5">
+        <v>2.2970000000000002</v>
+      </c>
+      <c r="Q9" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="B10" s="5">
+        <v>4</v>
+      </c>
+      <c r="C10" s="5">
+        <v>140946939</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.32540000000000002</v>
+      </c>
+      <c r="G10" s="5">
+        <v>9.9099999999999991E-7</v>
+      </c>
+      <c r="H10" s="5">
+        <v>1.1080000000000001</v>
+      </c>
+      <c r="I10" s="5">
+        <v>2.0889999999999999E-2</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="L10" s="5">
+        <v>5</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="N10" s="5">
+        <v>0</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P10" s="5">
+        <v>2.698</v>
+      </c>
+      <c r="Q10" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B11" s="5">
+        <v>6</v>
+      </c>
+      <c r="C11" s="5">
+        <v>139151017</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F11" s="5">
+        <v>3.671E-2</v>
+      </c>
+      <c r="G11" s="5">
+        <v>7.2300000000000002E-6</v>
+      </c>
+      <c r="H11" s="5">
+        <v>1.1919999999999999</v>
+      </c>
+      <c r="I11" s="5">
+        <v>3.9070000000000001E-2</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="L11" s="5">
+        <v>6</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>272</v>
+      </c>
+      <c r="N11" s="5">
+        <v>0</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P11" s="5">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="Q11" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="5">
+        <v>6</v>
+      </c>
+      <c r="C12" s="5">
+        <v>148149709</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.40279999999999999</v>
+      </c>
+      <c r="G12" s="5">
+        <v>7.8699999999999992E-6</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.91759999999999997</v>
+      </c>
+      <c r="I12" s="5">
+        <v>1.9230000000000001E-2</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="L12" s="5">
+        <v>7</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="N12" s="5">
+        <v>0</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="P12" s="5">
+        <v>3.5430000000000001</v>
+      </c>
+      <c r="Q12" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="B13" s="5">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5">
+        <v>135602416</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F13" s="5">
+        <v>7.5399999999999995E-2</v>
+      </c>
+      <c r="G13" s="5">
+        <v>4.1500000000000001E-6</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.85429999999999995</v>
+      </c>
+      <c r="I13" s="5">
+        <v>3.4200000000000001E-2</v>
+      </c>
+      <c r="J13" s="5">
+        <v>1</v>
+      </c>
+      <c r="K13" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="L13" s="5">
+        <v>8</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>276</v>
+      </c>
+      <c r="N13" s="5">
+        <v>8786</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P13" s="5">
+        <v>2.262</v>
+      </c>
+      <c r="Q13" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B14" s="5">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5">
+        <v>157162068</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F14" s="5">
+        <v>0.245</v>
+      </c>
+      <c r="G14" s="5">
+        <v>4.6600000000000003E-6</v>
+      </c>
+      <c r="H14" s="5">
+        <v>1.105</v>
+      </c>
+      <c r="I14" s="5">
+        <v>2.172E-2</v>
+      </c>
+      <c r="J14" s="5">
+        <v>1</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="L14" s="5">
+        <v>9</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>278</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="P14" s="5">
+        <v>1.1950000000000001</v>
+      </c>
+      <c r="Q14" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="B15" s="5">
+        <v>10</v>
+      </c>
+      <c r="C15" s="5">
+        <v>2364992</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F15" s="5">
+        <v>0.377</v>
+      </c>
+      <c r="G15" s="5">
+        <v>4.9599999999999999E-6</v>
+      </c>
+      <c r="H15" s="5">
+        <v>1.089</v>
+      </c>
+      <c r="I15" s="5">
+        <v>1.8749999999999999E-2</v>
+      </c>
+      <c r="J15" s="5">
+        <v>1</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="L15" s="5">
+        <v>10</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="N15" s="5">
+        <v>7722</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P15" s="5">
+        <v>2.375</v>
+      </c>
+      <c r="Q15" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="B16" s="5">
+        <v>10</v>
+      </c>
+      <c r="C16" s="5">
+        <v>15619054</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0.1052</v>
+      </c>
+      <c r="G16" s="5">
+        <v>5.4299999999999997E-6</v>
+      </c>
+      <c r="H16" s="5">
+        <v>1.1479999999999999</v>
+      </c>
+      <c r="I16" s="5">
+        <v>3.0360000000000002E-2</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>246</v>
+      </c>
+      <c r="L16" s="5">
+        <v>11</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="N16" s="5">
+        <v>0</v>
+      </c>
+      <c r="O16" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P16" s="5">
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="Q16" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="B17" s="5">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>77596104</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F17" s="5">
+        <v>8.0360000000000001E-2</v>
+      </c>
+      <c r="G17" s="5">
+        <v>5.1200000000000001E-6</v>
+      </c>
+      <c r="H17" s="5">
+        <v>1.153</v>
+      </c>
+      <c r="I17" s="5">
+        <v>3.1260000000000003E-2</v>
+      </c>
+      <c r="J17" s="5">
+        <v>1</v>
+      </c>
+      <c r="K17" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="L17" s="5">
+        <v>12</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="N17" s="5">
+        <v>0</v>
+      </c>
+      <c r="O17" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P17" s="5">
+        <v>2.246</v>
+      </c>
+      <c r="Q17" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="B18" s="43">
+        <v>16</v>
+      </c>
+      <c r="C18" s="43">
+        <v>60615067</v>
+      </c>
+      <c r="D18" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="F18" s="43">
+        <v>0.47720000000000001</v>
+      </c>
+      <c r="G18" s="43">
+        <v>4.9599999999999999E-6</v>
+      </c>
+      <c r="H18" s="43">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="I18" s="43">
+        <v>1.8839999999999999E-2</v>
+      </c>
+      <c r="J18" s="43">
+        <v>1</v>
+      </c>
+      <c r="K18" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="L18" s="43">
+        <v>13</v>
+      </c>
+      <c r="M18" s="43" t="s">
+        <v>283</v>
+      </c>
+      <c r="N18" s="43">
+        <v>57912</v>
+      </c>
+      <c r="O18" s="43" t="s">
+        <v>264</v>
+      </c>
+      <c r="P18" s="43">
+        <v>1.847</v>
+      </c>
+      <c r="Q18" s="43">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="B19" s="44"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="44"/>
+      <c r="P19" s="44"/>
+      <c r="Q19" s="44"/>
+    </row>
+    <row r="20" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D20" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E20" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="F20" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="G20" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="H20" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="I20" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="J20" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="K20" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="L20" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="M20" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="N20" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="O20" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q20" s="37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" s="43">
+        <v>10</v>
+      </c>
+      <c r="C21" s="43">
+        <v>23506529</v>
+      </c>
+      <c r="D21" s="43" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" s="43" t="s">
+        <v>262</v>
+      </c>
+      <c r="F21" s="43">
+        <v>0.13489999999999999</v>
+      </c>
+      <c r="G21" s="43">
+        <v>1.5200000000000001E-6</v>
+      </c>
+      <c r="H21" s="43">
+        <v>1.331</v>
+      </c>
+      <c r="I21" s="43">
+        <v>5.944E-2</v>
+      </c>
+      <c r="J21" s="43">
+        <v>1</v>
+      </c>
+      <c r="K21" s="43" t="s">
+        <v>286</v>
+      </c>
+      <c r="L21" s="43">
+        <v>1</v>
+      </c>
+      <c r="M21" s="43" t="s">
+        <v>287</v>
+      </c>
+      <c r="N21" s="43">
+        <v>0</v>
+      </c>
+      <c r="O21" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="P21" s="43">
+        <v>8.4320000000000004</v>
+      </c>
+      <c r="Q21" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="38" t="s">
+        <v>312</v>
+      </c>
+      <c r="B22" s="39"/>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="39"/>
+      <c r="H22" s="39"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="39"/>
+      <c r="K22" s="39"/>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="39"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+    </row>
+    <row r="23" spans="1:17" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="37" t="s">
+        <v>231</v>
+      </c>
+      <c r="B23" s="42" t="s">
+        <v>232</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>233</v>
+      </c>
+      <c r="D23" s="37" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="F23" s="37" t="s">
+        <v>251</v>
+      </c>
+      <c r="G23" s="37" t="s">
+        <v>252</v>
+      </c>
+      <c r="H23" s="37" t="s">
+        <v>284</v>
+      </c>
+      <c r="I23" s="37" t="s">
+        <v>285</v>
+      </c>
+      <c r="J23" s="37" t="s">
+        <v>253</v>
+      </c>
+      <c r="K23" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="L23" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="M23" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="N23" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="O23" s="37" t="s">
+        <v>258</v>
+      </c>
+      <c r="P23" s="37" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q23" s="37" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5">
+        <v>241294044</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F24" s="5">
+        <v>7.0440000000000003E-2</v>
+      </c>
+      <c r="G24" s="5">
+        <v>3.7790000000000002E-6</v>
+      </c>
+      <c r="H24" s="5">
+        <v>1.369</v>
+      </c>
+      <c r="I24" s="5">
+        <v>6.7989999999999995E-2</v>
+      </c>
+      <c r="J24" s="5">
+        <v>1</v>
+      </c>
+      <c r="K24" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="L24" s="5">
+        <v>1</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="N24" s="5">
+        <v>0</v>
+      </c>
+      <c r="O24" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P24" s="5">
+        <v>8.9480000000000004</v>
+      </c>
+      <c r="Q24" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="B25" s="5">
+        <v>2</v>
+      </c>
+      <c r="C25" s="5">
+        <v>176441451</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F25" s="5">
+        <v>0.41570000000000001</v>
+      </c>
+      <c r="G25" s="5">
+        <v>8.5569999999999996E-6</v>
+      </c>
+      <c r="H25" s="5">
+        <v>1.1679999999999999</v>
+      </c>
+      <c r="I25" s="5">
+        <v>3.4849999999999999E-2</v>
+      </c>
+      <c r="J25" s="5">
+        <v>1</v>
+      </c>
+      <c r="K25" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="L25" s="5">
+        <v>2</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>292</v>
+      </c>
+      <c r="N25" s="5">
+        <v>122082</v>
+      </c>
+      <c r="O25" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P25" s="5">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="Q25" s="5" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="B26" s="5">
+        <v>2</v>
+      </c>
+      <c r="C26" s="5">
+        <v>179065897</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="5">
+        <v>4.9599999999999998E-2</v>
+      </c>
+      <c r="G26" s="5">
+        <v>6.3629999999999999E-6</v>
+      </c>
+      <c r="H26" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="I26" s="5">
+        <v>6.3119999999999996E-2</v>
+      </c>
+      <c r="J26" s="5">
+        <v>1</v>
+      </c>
+      <c r="K26" s="5" t="s">
+        <v>293</v>
+      </c>
+      <c r="L26" s="5">
+        <v>3</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="N26" s="5">
+        <v>0</v>
+      </c>
+      <c r="O26" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P26" s="5">
+        <v>4.1479999999999997</v>
+      </c>
+      <c r="Q26" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="B27" s="5">
+        <v>4</v>
+      </c>
+      <c r="C27" s="5">
+        <v>114633364</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F27" s="5">
+        <v>0.25600000000000001</v>
+      </c>
+      <c r="G27" s="5">
+        <v>6.7939999999999997E-6</v>
+      </c>
+      <c r="H27" s="5">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="I27" s="5">
+        <v>3.8240000000000003E-2</v>
+      </c>
+      <c r="J27" s="5">
+        <v>1</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="L27" s="5">
+        <v>4</v>
+      </c>
+      <c r="M27" s="5" t="s">
+        <v>296</v>
+      </c>
+      <c r="N27" s="5">
+        <v>0</v>
+      </c>
+      <c r="O27" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P27" s="5">
+        <v>2.895</v>
+      </c>
+      <c r="Q27" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="B28" s="5">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>66152473</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F28" s="5">
+        <v>0.254</v>
+      </c>
+      <c r="G28" s="5">
+        <v>8.6160000000000002E-6</v>
+      </c>
+      <c r="H28" s="5">
+        <v>0.82489999999999997</v>
+      </c>
+      <c r="I28" s="5">
+        <v>4.326E-2</v>
+      </c>
+      <c r="J28" s="5">
+        <v>1</v>
+      </c>
+      <c r="K28" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="L28" s="5">
+        <v>5</v>
+      </c>
+      <c r="M28" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="N28" s="5">
+        <v>0</v>
+      </c>
+      <c r="O28" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P28" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="Q28" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B29" s="5">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>108246999</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="F29" s="5">
+        <v>7.1429999999999993E-2</v>
+      </c>
+      <c r="G29" s="5">
+        <v>2.4290000000000001E-8</v>
+      </c>
+      <c r="H29" s="5">
+        <v>1.3979999999999999</v>
+      </c>
+      <c r="I29" s="5">
+        <v>6.012E-2</v>
+      </c>
+      <c r="J29" s="5">
+        <v>1</v>
+      </c>
+      <c r="K29" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="L29" s="5">
+        <v>6</v>
+      </c>
+      <c r="M29" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="N29" s="5">
+        <v>0</v>
+      </c>
+      <c r="O29" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P29" s="5">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="Q29" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B30" s="5">
+        <v>8</v>
+      </c>
+      <c r="C30" s="5">
+        <v>19401149</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="F30" s="5">
+        <v>0.1429</v>
+      </c>
+      <c r="G30" s="5">
+        <v>7.5719999999999997E-6</v>
+      </c>
+      <c r="H30" s="5">
+        <v>1.2290000000000001</v>
+      </c>
+      <c r="I30" s="5">
+        <v>4.5969999999999997E-2</v>
+      </c>
+      <c r="J30" s="5">
+        <v>1</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="L30" s="5">
+        <v>7</v>
+      </c>
+      <c r="M30" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="N30" s="5">
+        <v>0</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P30" s="5">
+        <v>0.28499999999999998</v>
+      </c>
+      <c r="Q30" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B31" s="5">
+        <v>10</v>
+      </c>
+      <c r="C31" s="5">
+        <v>20715852</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F31" s="5">
+        <v>7.2419999999999998E-2</v>
+      </c>
+      <c r="G31" s="5">
+        <v>1.6649999999999999E-6</v>
+      </c>
+      <c r="H31" s="5">
+        <v>1.33</v>
+      </c>
+      <c r="I31" s="5">
+        <v>5.9540000000000003E-2</v>
+      </c>
+      <c r="J31" s="5">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="L31" s="5">
+        <v>8</v>
+      </c>
+      <c r="M31" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="N31" s="5">
+        <v>75822</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P31" s="5">
+        <v>3.048</v>
+      </c>
+      <c r="Q31" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B32" s="5">
+        <v>15</v>
+      </c>
+      <c r="C32" s="5">
+        <v>59389768</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F32" s="5">
+        <v>0.254</v>
+      </c>
+      <c r="G32" s="5">
+        <v>8.4789999999999996E-6</v>
+      </c>
+      <c r="H32" s="5">
+        <v>1.1890000000000001</v>
+      </c>
+      <c r="I32" s="5">
+        <v>3.8809999999999997E-2</v>
+      </c>
+      <c r="J32" s="5">
+        <v>1</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="L32" s="5">
+        <v>9</v>
+      </c>
+      <c r="M32" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N32" s="5">
+        <v>149</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="P32" s="5">
+        <v>2.2879999999999998</v>
+      </c>
+      <c r="Q32" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B33" s="5">
+        <v>18</v>
+      </c>
+      <c r="C33" s="5">
+        <v>8302561</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="F33" s="5">
+        <v>9.9210000000000007E-2</v>
+      </c>
+      <c r="G33" s="5">
+        <v>6.6930000000000001E-6</v>
+      </c>
+      <c r="H33" s="5">
+        <v>1.276</v>
+      </c>
+      <c r="I33" s="5">
+        <v>5.4179999999999999E-2</v>
+      </c>
+      <c r="J33" s="5">
+        <v>1</v>
+      </c>
+      <c r="K33" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="L33" s="5">
+        <v>10</v>
+      </c>
+      <c r="M33" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="N33" s="5">
+        <v>0</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="P33" s="5">
+        <v>2.4260000000000002</v>
+      </c>
+      <c r="Q33" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B34" s="5">
+        <v>19</v>
+      </c>
+      <c r="C34" s="5">
+        <v>29712441</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="F34" s="5">
+        <v>0.24110000000000001</v>
+      </c>
+      <c r="G34" s="5">
+        <v>9.7079999999999992E-6</v>
+      </c>
+      <c r="H34" s="5">
+        <v>0.82820000000000005</v>
+      </c>
+      <c r="I34" s="5">
+        <v>4.2619999999999998E-2</v>
+      </c>
+      <c r="J34" s="5">
+        <v>1</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="L34" s="5">
+        <v>11</v>
+      </c>
+      <c r="M34" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="N34" s="5">
+        <v>5718</v>
+      </c>
+      <c r="O34" s="5" t="s">
+        <v>264</v>
+      </c>
+      <c r="P34" s="5">
+        <v>2.7269999999999999</v>
+      </c>
+      <c r="Q34" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I35" s="4"/>
+    </row>
+    <row r="36" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I36" s="4"/>
+    </row>
+    <row r="37" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I38" s="4"/>
+    </row>
+    <row r="39" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I42" s="4"/>
+    </row>
+    <row r="43" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I43" s="4"/>
+    </row>
+    <row r="44" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I44" s="4"/>
+    </row>
+    <row r="45" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I45" s="4"/>
+    </row>
+    <row r="46" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I46" s="4"/>
+    </row>
+    <row r="47" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I47" s="4"/>
+    </row>
+    <row r="48" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="I48" s="4"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2092,38 +4144,38 @@
       <c r="N1" s="12"/>
     </row>
     <row r="2" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="52" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="51" t="s">
+      <c r="B2" s="53"/>
+      <c r="C2" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46" t="s">
+      <c r="D2" s="51"/>
+      <c r="E2" s="51" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="G2" s="51" t="s">
+      <c r="F2" s="57"/>
+      <c r="G2" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46" t="s">
+      <c r="H2" s="51"/>
+      <c r="I2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="J2" s="52"/>
-      <c r="K2" s="51" t="s">
+      <c r="J2" s="57"/>
+      <c r="K2" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46" t="s">
+      <c r="L2" s="51"/>
+      <c r="M2" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="N2" s="46"/>
+      <c r="N2" s="51"/>
     </row>
     <row r="3" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="49"/>
-      <c r="B3" s="50"/>
+      <c r="A3" s="54"/>
+      <c r="B3" s="55"/>
       <c r="C3" s="9" t="s">
         <v>1</v>
       </c>
@@ -2163,26 +4215,26 @@
       <c r="O3" s="26"/>
     </row>
     <row r="4" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="50" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="50"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="50"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="50"/>
+      <c r="N4" s="50"/>
       <c r="O4" s="26"/>
     </row>
     <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="47" t="s">
         <v>14</v>
       </c>
       <c r="B5" s="22" t="s">
@@ -2228,7 +4280,7 @@
       <c r="P5" s="36"/>
     </row>
     <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43"/>
+      <c r="A6" s="48"/>
       <c r="B6" s="23" t="s">
         <v>9</v>
       </c>
@@ -2272,7 +4324,7 @@
       <c r="P6" s="36"/>
     </row>
     <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="43"/>
+      <c r="A7" s="48"/>
       <c r="B7" s="23" t="s">
         <v>10</v>
       </c>
@@ -2316,7 +4368,7 @@
       <c r="P7" s="36"/>
     </row>
     <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="43"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="23" t="s">
         <v>11</v>
       </c>
@@ -2360,7 +4412,7 @@
       <c r="P8" s="36"/>
     </row>
     <row r="9" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="43"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="23" t="s">
         <v>12</v>
       </c>
@@ -2404,7 +4456,7 @@
       <c r="P9" s="36"/>
     </row>
     <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="48" t="s">
         <v>215</v>
       </c>
       <c r="B10" s="23" t="s">
@@ -2450,7 +4502,7 @@
       <c r="P10" s="36"/>
     </row>
     <row r="11" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="43"/>
+      <c r="A11" s="48"/>
       <c r="B11" s="23" t="s">
         <v>9</v>
       </c>
@@ -2494,7 +4546,7 @@
       <c r="P11" s="36"/>
     </row>
     <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="23" t="s">
         <v>10</v>
       </c>
@@ -2538,7 +4590,7 @@
       <c r="P12" s="36"/>
     </row>
     <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="43"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="23" t="s">
         <v>11</v>
       </c>
@@ -2582,7 +4634,7 @@
       <c r="P13" s="36"/>
     </row>
     <row r="14" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="24" t="s">
         <v>12</v>
       </c>
@@ -2626,27 +4678,27 @@
       <c r="P14" s="36"/>
     </row>
     <row r="15" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+      <c r="A15" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="45"/>
-      <c r="C15" s="45"/>
-      <c r="D15" s="45"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="45"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="45"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="45"/>
-      <c r="M15" s="45"/>
-      <c r="N15" s="45"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="50"/>
+      <c r="D15" s="50"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="50"/>
+      <c r="G15" s="50"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+      <c r="J15" s="50"/>
+      <c r="K15" s="50"/>
+      <c r="L15" s="50"/>
+      <c r="M15" s="50"/>
+      <c r="N15" s="50"/>
       <c r="O15" s="26"/>
       <c r="P15" s="36"/>
     </row>
     <row r="16" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="47" t="s">
         <v>14</v>
       </c>
       <c r="B16" s="22" t="s">
@@ -2692,7 +4744,7 @@
       <c r="P16" s="36"/>
     </row>
     <row r="17" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="43"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="23" t="s">
         <v>9</v>
       </c>
@@ -2736,7 +4788,7 @@
       <c r="P17" s="36"/>
     </row>
     <row r="18" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="43"/>
+      <c r="A18" s="48"/>
       <c r="B18" s="23" t="s">
         <v>10</v>
       </c>
@@ -2780,7 +4832,7 @@
       <c r="P18" s="36"/>
     </row>
     <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="43"/>
+      <c r="A19" s="48"/>
       <c r="B19" s="23" t="s">
         <v>11</v>
       </c>
@@ -2824,7 +4876,7 @@
       <c r="P19" s="36"/>
     </row>
     <row r="20" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="43"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="23" t="s">
         <v>12</v>
       </c>
@@ -2868,7 +4920,7 @@
       <c r="P20" s="36"/>
     </row>
     <row r="21" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="48" t="s">
         <v>215</v>
       </c>
       <c r="B21" s="23" t="s">
@@ -2914,7 +4966,7 @@
       <c r="P21" s="36"/>
     </row>
     <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="43"/>
+      <c r="A22" s="48"/>
       <c r="B22" s="23" t="s">
         <v>9</v>
       </c>
@@ -2958,7 +5010,7 @@
       <c r="P22" s="36"/>
     </row>
     <row r="23" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="43"/>
+      <c r="A23" s="48"/>
       <c r="B23" s="23" t="s">
         <v>10</v>
       </c>
@@ -3002,7 +5054,7 @@
       <c r="P23" s="36"/>
     </row>
     <row r="24" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="43"/>
+      <c r="A24" s="48"/>
       <c r="B24" s="23" t="s">
         <v>11</v>
       </c>
@@ -3045,7 +5097,7 @@
       <c r="P24" s="36"/>
     </row>
     <row r="25" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="44"/>
+      <c r="A25" s="49"/>
       <c r="B25" s="24" t="s">
         <v>12</v>
       </c>
@@ -3088,26 +5140,26 @@
       <c r="P25" s="36"/>
     </row>
     <row r="26" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="45" t="s">
+      <c r="A26" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
-      <c r="D26" s="45"/>
-      <c r="E26" s="45"/>
-      <c r="F26" s="45"/>
-      <c r="G26" s="45"/>
-      <c r="H26" s="45"/>
-      <c r="I26" s="45"/>
-      <c r="J26" s="45"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="45"/>
-      <c r="M26" s="45"/>
-      <c r="N26" s="45"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="50"/>
+      <c r="D26" s="50"/>
+      <c r="E26" s="50"/>
+      <c r="F26" s="50"/>
+      <c r="G26" s="50"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="50"/>
+      <c r="J26" s="50"/>
+      <c r="K26" s="50"/>
+      <c r="L26" s="50"/>
+      <c r="M26" s="50"/>
+      <c r="N26" s="50"/>
       <c r="P26" s="36"/>
     </row>
     <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="47" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="22" t="s">
@@ -3152,7 +5204,7 @@
       <c r="P27" s="36"/>
     </row>
     <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="43"/>
+      <c r="A28" s="48"/>
       <c r="B28" s="23" t="s">
         <v>9</v>
       </c>
@@ -3195,7 +5247,7 @@
       <c r="P28" s="36"/>
     </row>
     <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="43"/>
+      <c r="A29" s="48"/>
       <c r="B29" s="23" t="s">
         <v>10</v>
       </c>
@@ -3238,7 +5290,7 @@
       <c r="P29" s="36"/>
     </row>
     <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="43"/>
+      <c r="A30" s="48"/>
       <c r="B30" s="23" t="s">
         <v>11</v>
       </c>
@@ -3281,7 +5333,7 @@
       <c r="P30" s="36"/>
     </row>
     <row r="31" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="43"/>
+      <c r="A31" s="48"/>
       <c r="B31" s="23" t="s">
         <v>12</v>
       </c>
@@ -3324,7 +5376,7 @@
       <c r="P31" s="36"/>
     </row>
     <row r="32" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="43" t="s">
+      <c r="A32" s="48" t="s">
         <v>215</v>
       </c>
       <c r="B32" s="23" t="s">
@@ -3369,7 +5421,7 @@
       <c r="P32" s="36"/>
     </row>
     <row r="33" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="43"/>
+      <c r="A33" s="48"/>
       <c r="B33" s="23" t="s">
         <v>9</v>
       </c>
@@ -3412,7 +5464,7 @@
       <c r="P33" s="36"/>
     </row>
     <row r="34" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="43"/>
+      <c r="A34" s="48"/>
       <c r="B34" s="23" t="s">
         <v>10</v>
       </c>
@@ -3455,7 +5507,7 @@
       <c r="P34" s="36"/>
     </row>
     <row r="35" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="43"/>
+      <c r="A35" s="48"/>
       <c r="B35" s="23" t="s">
         <v>11</v>
       </c>
@@ -3498,7 +5550,7 @@
       <c r="P35" s="36"/>
     </row>
     <row r="36" spans="1:16" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="44"/>
+      <c r="A36" s="49"/>
       <c r="B36" s="24" t="s">
         <v>12</v>
       </c>
